--- a/output/graficos_nacionales/plot_nacional_d_residentes_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_residentes_a_2024.xlsx
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:42</t>
+    <t xml:space="preserve">2026-09-08 10:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
